--- a/results/Int All Data 0.4/Rando_5_permute.xlsx
+++ b/results/Int All Data 0.4/Rando_5_permute.xlsx
@@ -440,1547 +440,1547 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8036239401438449</v>
+        <v>0.8022701061160148</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8039397961135226</v>
+        <v>0.8013526749233542</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8027366456675573</v>
+        <v>0.8016383941766592</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8027366456675573</v>
+        <v>0.8016383941766592</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8058650686479626</v>
+        <v>0.8016383941766592</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.798360446718865</v>
+        <v>0.8003749702979478</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8014285962665245</v>
+        <v>0.801954250146337</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8011127402968466</v>
+        <v>0.8029319547717433</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8014285962665245</v>
+        <v>0.8013526749233542</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7971572962728996</v>
+        <v>0.8018939767135911</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7965557210499168</v>
+        <v>0.8012622647742355</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7965557210499168</v>
+        <v>0.7985099711962538</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7971874329892725</v>
+        <v>0.797878259256898</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7970970228401537</v>
+        <v>0.7927944270256799</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8007064741780501</v>
+        <v>0.7893501480755968</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7933368879203927</v>
+        <v>0.7902675792682574</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7924194567277321</v>
+        <v>0.7905834352379352</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7921337374744273</v>
+        <v>0.7905532985215622</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7939384631433755</v>
+        <v>0.7905532985215622</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7905544576260382</v>
+        <v>0.7936214480692217</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7963749007516793</v>
+        <v>0.7926738801601882</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7975479144812718</v>
+        <v>0.7926738801601882</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.797232058511594</v>
+        <v>0.7995624380603545</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7954273328426458</v>
+        <v>0.8010513077596249</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7935924704573247</v>
+        <v>0.8007354517899471</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7953670594098999</v>
+        <v>0.7998782940300324</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7941639089639345</v>
+        <v>0.802179695966896</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7941639089639345</v>
+        <v>0.8018939767135911</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7944797649336124</v>
+        <v>0.797878259256898</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7892608970309538</v>
+        <v>0.7981941152265759</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7851704173355666</v>
+        <v>0.7991115464192365</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7992778779115255</v>
+        <v>0.8009464088045577</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8026317467124899</v>
+        <v>0.7991115464192365</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8065570540200642</v>
+        <v>0.7987956904495587</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7631822054280862</v>
+        <v>0.7984798344798809</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7671376494520334</v>
+        <v>0.8005100059693881</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7643853558740517</v>
+        <v>0.8001640132833373</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7643853558740517</v>
+        <v>0.8054130179023686</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7662648437816943</v>
+        <v>0.785892539424041</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7665806997513721</v>
+        <v>0.785892539424041</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7661744336325755</v>
+        <v>0.7773789170486882</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7661744336325755</v>
+        <v>0.7770630610790104</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7667458721391853</v>
+        <v>0.7752281986936893</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7634209809501179</v>
+        <v>0.7643662306501997</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7761746074982468</v>
+        <v>0.7630280445327939</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7768063194376025</v>
+        <v>0.7412942560577698</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7768063194376025</v>
+        <v>0.7293520026427582</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7643830376651</v>
+        <v>0.7198316980301019</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7643830376651</v>
+        <v>0.7164320446023402</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7611798524460003</v>
+        <v>0.7039931149194133</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7569989626014941</v>
+        <v>0.7058279773047345</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7583226599129513</v>
+        <v>0.6950286009029424</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7568337902136809</v>
+        <v>0.6857337421108451</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7463804064979397</v>
+        <v>0.6926825734437574</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7526975258914963</v>
+        <v>0.6938857238897228</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7478246506748886</v>
+        <v>0.6744075527247648</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7525624902200561</v>
+        <v>0.668722145270564</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7507276278347349</v>
+        <v>0.6764678609306449</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7451024938132799</v>
+        <v>0.6720458773551554</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7318064063704381</v>
+        <v>0.6698951590001565</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.740123560537129</v>
+        <v>0.6793708380904913</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7375665760633334</v>
+        <v>0.681191211669864</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7375665760633334</v>
+        <v>0.6890876109118096</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7379728421821301</v>
+        <v>0.6780326519730856</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7379728421821301</v>
+        <v>0.6868766191240647</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7260462366775429</v>
+        <v>0.6853274759920485</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.723670072501985</v>
+        <v>0.6828910383837448</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7334459596515732</v>
+        <v>0.6886813447930129</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7316110972662521</v>
+        <v>0.6889972007626908</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7075023037201458</v>
+        <v>0.7035868488006166</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7075023037201458</v>
+        <v>0.6954047303053661</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6938915194121023</v>
+        <v>0.698744110300382</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6938915194121023</v>
+        <v>0.6774310767501028</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6960121010507282</v>
+        <v>0.6843955559934395</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.694236352993677</v>
+        <v>0.6847114119631172</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.694236352993677</v>
+        <v>0.6822749743548134</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6892574197175263</v>
+        <v>0.6763339843636806</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6881748161370524</v>
+        <v>0.6731754246669024</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6749534909329052</v>
+        <v>0.6648884072165844</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6749534909329052</v>
+        <v>0.6642566952772289</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6549004039479098</v>
+        <v>0.6886523671811158</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6312112062220728</v>
+        <v>0.682200212116119</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6357983621853756</v>
+        <v>0.6583603308084174</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.516433783259054</v>
+        <v>0.6470497893327616</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5068074205868547</v>
+        <v>0.6132230638608611</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5375057230783497</v>
+        <v>0.588691197181058</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5423194839666874</v>
+        <v>0.5976858479139018</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5338817829345048</v>
+        <v>0.5980017038835795</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5393116078517737</v>
+        <v>0.564097897964033</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.5498252650002609</v>
+        <v>0.5606837557303228</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5585643331961727</v>
+        <v>0.5582015334952216</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5585643331961727</v>
+        <v>0.5448451726196341</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5569850533477836</v>
+        <v>0.5298324514480113</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5656337113945766</v>
+        <v>0.5314117312964004</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5476745466452618</v>
+        <v>0.5384353248680069</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5601882385668833</v>
+        <v>0.5037079752183463</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5019188974598225</v>
+        <v>0.5039322619344294</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.4993920497023999</v>
+        <v>0.4879429952418761</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5011220131326537</v>
+        <v>0.4896260149408567</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.4864529664381299</v>
+        <v>0.4867844703182321</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.4995224489559367</v>
+        <v>0.4698934203434427</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5002590598503597</v>
+        <v>0.4662236955728005</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.4920757822506332</v>
+        <v>0.4677427019884438</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.4945423565753099</v>
+        <v>0.477518589138032</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.4945423565753099</v>
+        <v>0.4748567057091691</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.4964374923933769</v>
+        <v>0.4681935936295618</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.4973549235860374</v>
+        <v>0.4660573640805114</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5064544732739485</v>
+        <v>0.4684190394501208</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5045593374558816</v>
+        <v>0.4815789321170464</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5051006392461185</v>
+        <v>0.4856526047975335</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.4413168585950495</v>
+        <v>0.4856526047975335</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.4413168585950495</v>
+        <v>0.487698424197465</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.4581308281221928</v>
+        <v>0.4882999994204478</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.4532579529055851</v>
+        <v>0.4628686676673602</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.4532579529055851</v>
+        <v>0.4643876740830035</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.457078361258092</v>
+        <v>0.4286826198079364</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.4342341506951729</v>
+        <v>0.4271636133922931</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.4271502836908205</v>
+        <v>0.4271636133922931</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.4098842634180832</v>
+        <v>0.427479469361971</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.4118541614748445</v>
+        <v>0.4359015224837291</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.3657728039316824</v>
+        <v>0.4122291317727924</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.34217517545944</v>
+        <v>0.3964241626919043</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.3834885567410619</v>
+        <v>0.4291056929416333</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.4591085327475992</v>
+        <v>0.4237674372779591</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.4591085327475992</v>
+        <v>0.4237674372779591</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.4441137776953526</v>
+        <v>0.4253467171263482</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4442488133667928</v>
+        <v>0.4239024729493993</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4450758344103346</v>
+        <v>0.3818090143555089</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4661611039311029</v>
+        <v>0.4424040985934267</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.48071945614818</v>
+        <v>0.4424040985934267</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4800576074924514</v>
+        <v>0.4454421114247133</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4799370606269596</v>
+        <v>0.5074646328246797</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.4817116495795348</v>
+        <v>0.5124557366978273</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4847797991271944</v>
+        <v>0.5070114229746098</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4878178119584809</v>
+        <v>0.5097034431198456</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4842083606205846</v>
+        <v>0.510966866998557</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4842083606205846</v>
+        <v>0.510966866998557</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4842083606205846</v>
+        <v>0.510966866998557</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4960746926924258</v>
+        <v>0.5050270361118999</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4979095550777469</v>
+        <v>0.4962734791100396</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.499744417463068</v>
+        <v>0.5007702249242236</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4927208238914614</v>
+        <v>0.4810219824163851</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4933223991144442</v>
+        <v>0.4821949961459777</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4933223991144442</v>
+        <v>0.4904362289694982</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4924049679217836</v>
+        <v>0.4913837968785317</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4949318156792062</v>
+        <v>0.4913837968785317</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4954429807530702</v>
+        <v>0.4925869473244971</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.4960445559760529</v>
+        <v>0.4925869473244971</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5006317119393556</v>
+        <v>0.5457747744092913</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5</v>
+        <v>0.5457747744092913</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5</v>
+        <v>0.5524523752948473</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4990825688073395</v>
+        <v>0.5524523752948473</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4993984247770173</v>
+        <v>0.5233982625023906</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4993984247770173</v>
+        <v>0.5012135823862485</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5003158559696779</v>
+        <v>0.4958138941853524</v>
       </c>
     </row>
   </sheetData>
